--- a/outputs/50631.xlsx
+++ b/outputs/50631.xlsx
@@ -39,7 +39,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,6 +61,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -118,7 +124,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -127,11 +133,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -327,7 +337,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:J38"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.43"/>
@@ -337,661 +347,894 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.86"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="n">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3" t="n">
         <v>44440</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3" t="n">
         <v>44530</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J5" s="2" t="n">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="3" t="n">
         <v>44452</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J6" s="2" t="n">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="3" t="n">
         <v>44453</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="n">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B7)-1&lt;=$F$3,$B$3+ROWS($B$7:$B7)-1,"")</f>
         <v>44440</v>
       </c>
-      <c r="C7" s="1" t="str">
+      <c r="C7" s="2" t="str">
         <f aca="false">IFERROR(INDEX(#ref!,MATCH(B7,#ref!,0)),"")</f>
         <v/>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D38)-1&lt;=$F$3,$B$3+ROWS($B$7:$D38)-1,"")</f>
         <v>44471</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="E7" s="2"/>
+      <c r="F7" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($D$7:$F38)-1&lt;=$F$3,$B$3+ROWS($D$7:$F38)-1,"")</f>
         <v>44471</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="G7" s="2"/>
+      <c r="H7" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B7)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B7)-1,$J$5:$J$7),"")</f>
         <v>44440</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="I7" s="2"/>
+      <c r="J7" s="3" t="n">
         <v>44470</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="n">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B8)-1&lt;=$F$3,$B$3+ROWS($B$7:$B8)-1,"")</f>
         <v>44441</v>
       </c>
-      <c r="C8" s="1" t="str">
+      <c r="C8" s="2" t="str">
         <f aca="false">IFERROR(INDEX(#ref!,MATCH(B8,#ref!,0)),"")</f>
         <v/>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D39)-1&lt;=$F$3,$B$3+ROWS($B$7:$D39)-1,"")</f>
         <v>44472</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="E8" s="2"/>
+      <c r="F8" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F39)-1&lt;=$F$3,$B$3+ROWS($B$7:$F39)-1,"")</f>
         <v>44472</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="G8" s="2"/>
+      <c r="H8" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B8)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B8)-1,$J$5:$J$7),"")</f>
         <v>44441</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="n">
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B9)-1&lt;=$F$3,$B$3+ROWS($B$7:$B9)-1,"")</f>
         <v>44442</v>
       </c>
-      <c r="C9" s="1" t="str">
+      <c r="C9" s="2" t="str">
         <f aca="false">IFERROR(INDEX(#ref!,MATCH(B9,#ref!,0)),"")</f>
         <v/>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D40)-1&lt;=$F$3,$B$3+ROWS($B$7:$D40)-1,"")</f>
         <v>44473</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="E9" s="2"/>
+      <c r="F9" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F40)-1&lt;=$F$3,$B$3+ROWS($B$7:$F40)-1,"")</f>
         <v>44473</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="G9" s="2"/>
+      <c r="H9" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B9)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B9)-1,$J$5:$J$7),"")</f>
         <v>44442</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="n">
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B10)-1&lt;=$F$3,$B$3+ROWS($B$7:$B10)-1,"")</f>
         <v>44443</v>
       </c>
-      <c r="C10" s="1" t="str">
+      <c r="C10" s="2" t="str">
         <f aca="false">IFERROR(INDEX(#ref!,MATCH(B10,#ref!,0)),"")</f>
         <v/>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D41)-1&lt;=$F$3,$B$3+ROWS($B$7:$D41)-1,"")</f>
         <v>44474</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="E10" s="2"/>
+      <c r="F10" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F41)-1&lt;=$F$3,$B$3+ROWS($B$7:$F41)-1,"")</f>
         <v>44474</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="G10" s="2"/>
+      <c r="H10" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B10)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B10)-1,$J$5:$J$7),"")</f>
         <v>44445</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="n">
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B11)-1&lt;=$F$3,$B$3+ROWS($B$7:$B11)-1,"")</f>
         <v>44444</v>
       </c>
-      <c r="C11" s="1" t="str">
+      <c r="C11" s="2" t="str">
         <f aca="false">IFERROR(INDEX(#ref!,MATCH(B11,#ref!,0)),"")</f>
         <v/>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D42)-1&lt;=$F$3,$B$3+ROWS($B$7:$D42)-1,"")</f>
         <v>44475</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="E11" s="2"/>
+      <c r="F11" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F42)-1&lt;=$F$3,$B$3+ROWS($B$7:$F42)-1,"")</f>
         <v>44475</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="G11" s="2"/>
+      <c r="H11" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B11)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B11)-1,$J$5:$J$7),"")</f>
         <v>44446</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="n">
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B12)-1&lt;=$F$3,$B$3+ROWS($B$7:$B12)-1,"")</f>
         <v>44445</v>
       </c>
-      <c r="C12" s="1" t="str">
+      <c r="C12" s="2" t="str">
         <f aca="false">IFERROR(INDEX(#ref!,MATCH(B12,#ref!,0)),"")</f>
         <v/>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D43)-1&lt;=$F$3,$B$3+ROWS($B$7:$D43)-1,"")</f>
         <v>44476</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="E12" s="2"/>
+      <c r="F12" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F43)-1&lt;=$F$3,$B$3+ROWS($B$7:$F43)-1,"")</f>
         <v>44476</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="G12" s="2"/>
+      <c r="H12" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B12)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B12)-1,$J$5:$J$7),"")</f>
         <v>44447</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="n">
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B13)-1&lt;=$F$3,$B$3+ROWS($B$7:$B13)-1,"")</f>
         <v>44446</v>
       </c>
-      <c r="C13" s="1" t="str">
+      <c r="C13" s="2" t="str">
         <f aca="false">IFERROR(INDEX(#ref!,MATCH(B13,#ref!,0)),"")</f>
         <v/>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D44)-1&lt;=$F$3,$B$3+ROWS($B$7:$D44)-1,"")</f>
         <v>44477</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="E13" s="2"/>
+      <c r="F13" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F44)-1&lt;=$F$3,$B$3+ROWS($B$7:$F44)-1,"")</f>
         <v>44477</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="G13" s="2"/>
+      <c r="H13" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B13)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B13)-1,$J$5:$J$7),"")</f>
         <v>44448</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="n">
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B14)-1&lt;=$F$3,$B$3+ROWS($B$7:$B14)-1,"")</f>
         <v>44447</v>
       </c>
-      <c r="C14" s="1" t="str">
+      <c r="C14" s="2" t="str">
         <f aca="false">IFERROR(INDEX(#ref!,MATCH(B14,#ref!,0)),"")</f>
         <v/>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D45)-1&lt;=$F$3,$B$3+ROWS($B$7:$D45)-1,"")</f>
         <v>44478</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="E14" s="2"/>
+      <c r="F14" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F45)-1&lt;=$F$3,$B$3+ROWS($B$7:$F45)-1,"")</f>
         <v>44478</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="G14" s="2"/>
+      <c r="H14" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B14)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B14)-1,$J$5:$J$7),"")</f>
         <v>44449</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="n">
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B15)-1&lt;=$F$3,$B$3+ROWS($B$7:$B15)-1,"")</f>
         <v>44448</v>
       </c>
-      <c r="C15" s="1" t="str">
+      <c r="C15" s="2" t="str">
         <f aca="false">IFERROR(INDEX(#ref!,MATCH(B15,#ref!,0)),"")</f>
         <v/>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D46)-1&lt;=$F$3,$B$3+ROWS($B$7:$D46)-1,"")</f>
         <v>44479</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="E15" s="2"/>
+      <c r="F15" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F46)-1&lt;=$F$3,$B$3+ROWS($B$7:$F46)-1,"")</f>
         <v>44479</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="G15" s="2"/>
+      <c r="H15" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B15)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B15)-1,$J$5:$J$7),"")</f>
         <v>44454</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="n">
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B16)-1&lt;=$F$3,$B$3+ROWS($B$7:$B16)-1,"")</f>
         <v>44449</v>
       </c>
-      <c r="C16" s="1" t="str">
+      <c r="C16" s="2" t="str">
         <f aca="false">IFERROR(INDEX(#ref!,MATCH(B16,#ref!,0)),"")</f>
         <v/>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D47)-1&lt;=$F$3,$B$3+ROWS($B$7:$D47)-1,"")</f>
         <v>44480</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="E16" s="2"/>
+      <c r="F16" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F47)-1&lt;=$F$3,$B$3+ROWS($B$7:$F47)-1,"")</f>
         <v>44480</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="G16" s="2"/>
+      <c r="H16" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B16)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B16)-1,$J$5:$J$7),"")</f>
         <v>44455</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="n">
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B17)-1&lt;=$F$3,$B$3+ROWS($B$7:$B17)-1,"")</f>
         <v>44450</v>
       </c>
-      <c r="C17" s="1" t="str">
+      <c r="C17" s="2" t="str">
         <f aca="false">IFERROR(INDEX(#ref!,MATCH(B17,#ref!,0)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D48)-1&lt;=$F$3,$B$3+ROWS($B$7:$D48)-1,"")</f>
         <v>44481</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="E17" s="2"/>
+      <c r="F17" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F48)-1&lt;=$F$3,$B$3+ROWS($B$7:$F48)-1,"")</f>
         <v>44481</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="G17" s="2"/>
+      <c r="H17" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B17)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B17)-1,$J$5:$J$7),"")</f>
         <v>44456</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="n">
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B18)-1&lt;=$F$3,$B$3+ROWS($B$7:$B18)-1,"")</f>
         <v>44451</v>
       </c>
-      <c r="C18" s="1" t="str">
+      <c r="C18" s="2" t="str">
         <f aca="false">IFERROR(INDEX(#ref!,MATCH(B18,#ref!,0)),"")</f>
         <v/>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D49)-1&lt;=$F$3,$B$3+ROWS($B$7:$D49)-1,"")</f>
         <v>44482</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="E18" s="2"/>
+      <c r="F18" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F49)-1&lt;=$F$3,$B$3+ROWS($B$7:$F49)-1,"")</f>
         <v>44482</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="G18" s="2"/>
+      <c r="H18" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B18)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B18)-1,$J$5:$J$7),"")</f>
         <v>44459</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="n">
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B19)-1&lt;=$F$3,$B$3+ROWS($B$7:$B19)-1,"")</f>
         <v>44452</v>
       </c>
-      <c r="C19" s="1" t="str">
+      <c r="C19" s="2" t="str">
         <f aca="false">IFERROR(INDEX(#ref!,MATCH(B19,#ref!,0)),"")</f>
         <v/>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D50)-1&lt;=$F$3,$B$3+ROWS($B$7:$D50)-1,"")</f>
         <v>44483</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="E19" s="2"/>
+      <c r="F19" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F50)-1&lt;=$F$3,$B$3+ROWS($B$7:$F50)-1,"")</f>
         <v>44483</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="G19" s="2"/>
+      <c r="H19" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B19)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B19)-1,$J$5:$J$7),"")</f>
         <v>44460</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="n">
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B20)-1&lt;=$F$3,$B$3+ROWS($B$7:$B20)-1,"")</f>
         <v>44453</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="C20" s="2"/>
+      <c r="D20" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D51)-1&lt;=$F$3,$B$3+ROWS($B$7:$D51)-1,"")</f>
         <v>44484</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="E20" s="2"/>
+      <c r="F20" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F51)-1&lt;=$F$3,$B$3+ROWS($B$7:$F51)-1,"")</f>
         <v>44484</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="G20" s="2"/>
+      <c r="H20" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B20)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B20)-1,$J$5:$J$7),"")</f>
         <v>44461</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3" t="n">
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B21)-1&lt;=$F$3,$B$3+ROWS($B$7:$B21)-1,"")</f>
         <v>44454</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="C21" s="2"/>
+      <c r="D21" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D52)-1&lt;=$F$3,$B$3+ROWS($B$7:$D52)-1,"")</f>
         <v>44485</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="E21" s="2"/>
+      <c r="F21" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F52)-1&lt;=$F$3,$B$3+ROWS($B$7:$F52)-1,"")</f>
         <v>44485</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="G21" s="2"/>
+      <c r="H21" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B21)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B21)-1,$J$5:$J$7),"")</f>
         <v>44462</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="n">
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B22)-1&lt;=$F$3,$B$3+ROWS($B$7:$B22)-1,"")</f>
         <v>44455</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="C22" s="2"/>
+      <c r="D22" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D53)-1&lt;=$F$3,$B$3+ROWS($B$7:$D53)-1,"")</f>
         <v>44486</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="E22" s="2"/>
+      <c r="F22" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F53)-1&lt;=$F$3,$B$3+ROWS($B$7:$F53)-1,"")</f>
         <v>44486</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="G22" s="2"/>
+      <c r="H22" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B22)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B22)-1,$J$5:$J$7),"")</f>
         <v>44463</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="3" t="n">
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B23)-1&lt;=$F$3,$B$3+ROWS($B$7:$B23)-1,"")</f>
         <v>44456</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="C23" s="2"/>
+      <c r="D23" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D54)-1&lt;=$F$3,$B$3+ROWS($B$7:$D54)-1,"")</f>
         <v>44487</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="E23" s="2"/>
+      <c r="F23" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F54)-1&lt;=$F$3,$B$3+ROWS($B$7:$F54)-1,"")</f>
         <v>44487</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="G23" s="2"/>
+      <c r="H23" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B23)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B23)-1,$J$5:$J$7),"")</f>
         <v>44466</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="n">
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B24)-1&lt;=$F$3,$B$3+ROWS($B$7:$B24)-1,"")</f>
         <v>44457</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="C24" s="2"/>
+      <c r="D24" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D55)-1&lt;=$F$3,$B$3+ROWS($B$7:$D55)-1,"")</f>
         <v>44488</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="E24" s="2"/>
+      <c r="F24" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F55)-1&lt;=$F$3,$B$3+ROWS($B$7:$F55)-1,"")</f>
         <v>44488</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="G24" s="2"/>
+      <c r="H24" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B24)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B24)-1,$J$5:$J$7),"")</f>
         <v>44467</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3" t="n">
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B25)-1&lt;=$F$3,$B$3+ROWS($B$7:$B25)-1,"")</f>
         <v>44458</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="C25" s="2"/>
+      <c r="D25" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D56)-1&lt;=$F$3,$B$3+ROWS($B$7:$D56)-1,"")</f>
         <v>44489</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="E25" s="2"/>
+      <c r="F25" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F56)-1&lt;=$F$3,$B$3+ROWS($B$7:$F56)-1,"")</f>
         <v>44489</v>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="G25" s="2"/>
+      <c r="H25" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B25)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B25)-1,$J$5:$J$7),"")</f>
         <v>44468</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3" t="n">
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B26)-1&lt;=$F$3,$B$3+ROWS($B$7:$B26)-1,"")</f>
         <v>44459</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="C26" s="2"/>
+      <c r="D26" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D57)-1&lt;=$F$3,$B$3+ROWS($B$7:$D57)-1,"")</f>
         <v>44490</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="E26" s="2"/>
+      <c r="F26" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F57)-1&lt;=$F$3,$B$3+ROWS($B$7:$F57)-1,"")</f>
         <v>44490</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="G26" s="2"/>
+      <c r="H26" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B26)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B26)-1,$J$5:$J$7),"")</f>
         <v>44469</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="3" t="n">
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B27)-1&lt;=$F$3,$B$3+ROWS($B$7:$B27)-1,"")</f>
         <v>44460</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="C27" s="2"/>
+      <c r="D27" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D58)-1&lt;=$F$3,$B$3+ROWS($B$7:$D58)-1,"")</f>
         <v>44491</v>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="E27" s="2"/>
+      <c r="F27" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F58)-1&lt;=$F$3,$B$3+ROWS($B$7:$F58)-1,"")</f>
         <v>44491</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="G27" s="2"/>
+      <c r="H27" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B27)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B27)-1,$J$5:$J$7),"")</f>
         <v>44473</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="3" t="n">
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B28)-1&lt;=$F$3,$B$3+ROWS($B$7:$B28)-1,"")</f>
         <v>44461</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="C28" s="2"/>
+      <c r="D28" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D59)-1&lt;=$F$3,$B$3+ROWS($B$7:$D59)-1,"")</f>
         <v>44492</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="E28" s="2"/>
+      <c r="F28" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F59)-1&lt;=$F$3,$B$3+ROWS($B$7:$F59)-1,"")</f>
         <v>44492</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="G28" s="2"/>
+      <c r="H28" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B28)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B28)-1,$J$5:$J$7),"")</f>
         <v>44474</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="3" t="n">
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B29)-1&lt;=$F$3,$B$3+ROWS($B$7:$B29)-1,"")</f>
         <v>44462</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="C29" s="2"/>
+      <c r="D29" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D60)-1&lt;=$F$3,$B$3+ROWS($B$7:$D60)-1,"")</f>
         <v>44493</v>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="E29" s="2"/>
+      <c r="F29" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F60)-1&lt;=$F$3,$B$3+ROWS($B$7:$F60)-1,"")</f>
         <v>44493</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="G29" s="2"/>
+      <c r="H29" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B29)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B29)-1,$J$5:$J$7),"")</f>
         <v>44475</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="3" t="n">
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B30)-1&lt;=$F$3,$B$3+ROWS($B$7:$B30)-1,"")</f>
         <v>44463</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="C30" s="2"/>
+      <c r="D30" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D61)-1&lt;=$F$3,$B$3+ROWS($B$7:$D61)-1,"")</f>
         <v>44494</v>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="E30" s="2"/>
+      <c r="F30" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F61)-1&lt;=$F$3,$B$3+ROWS($B$7:$F61)-1,"")</f>
         <v>44494</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="G30" s="2"/>
+      <c r="H30" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B30)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B30)-1,$J$5:$J$7),"")</f>
         <v>44476</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="3" t="n">
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B31)-1&lt;=$F$3,$B$3+ROWS($B$7:$B31)-1,"")</f>
         <v>44464</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="C31" s="2"/>
+      <c r="D31" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D62)-1&lt;=$F$3,$B$3+ROWS($B$7:$D62)-1,"")</f>
         <v>44495</v>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="E31" s="2"/>
+      <c r="F31" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F62)-1&lt;=$F$3,$B$3+ROWS($B$7:$F62)-1,"")</f>
         <v>44495</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="G31" s="2"/>
+      <c r="H31" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B31)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B31)-1,$J$5:$J$7),"")</f>
         <v>44477</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="3" t="n">
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B32)-1&lt;=$F$3,$B$3+ROWS($B$7:$B32)-1,"")</f>
         <v>44465</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="C32" s="2"/>
+      <c r="D32" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D63)-1&lt;=$F$3,$B$3+ROWS($B$7:$D63)-1,"")</f>
         <v>44496</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="E32" s="2"/>
+      <c r="F32" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F63)-1&lt;=$F$3,$B$3+ROWS($B$7:$F63)-1,"")</f>
         <v>44496</v>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="G32" s="2"/>
+      <c r="H32" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B32)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B32)-1,$J$5:$J$7),"")</f>
         <v>44480</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="3" t="n">
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B33)-1&lt;=$F$3,$B$3+ROWS($B$7:$B33)-1,"")</f>
         <v>44466</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="C33" s="2"/>
+      <c r="D33" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D64)-1&lt;=$F$3,$B$3+ROWS($B$7:$D64)-1,"")</f>
         <v>44497</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="E33" s="2"/>
+      <c r="F33" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F64)-1&lt;=$F$3,$B$3+ROWS($B$7:$F64)-1,"")</f>
         <v>44497</v>
       </c>
-      <c r="H33" s="3" t="n">
+      <c r="G33" s="2"/>
+      <c r="H33" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B33)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B33)-1,$J$5:$J$7),"")</f>
         <v>44481</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="3" t="n">
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B34)-1&lt;=$F$3,$B$3+ROWS($B$7:$B34)-1,"")</f>
         <v>44467</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="C34" s="2"/>
+      <c r="D34" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D65)-1&lt;=$F$3,$B$3+ROWS($B$7:$D65)-1,"")</f>
         <v>44498</v>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="E34" s="2"/>
+      <c r="F34" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F65)-1&lt;=$F$3,$B$3+ROWS($B$7:$F65)-1,"")</f>
         <v>44498</v>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="G34" s="2"/>
+      <c r="H34" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B34)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B34)-1,$J$5:$J$7),"")</f>
         <v>44482</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="3" t="n">
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B35)-1&lt;=$F$3,$B$3+ROWS($B$7:$B35)-1,"")</f>
         <v>44468</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="C35" s="2"/>
+      <c r="D35" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D66)-1&lt;=$F$3,$B$3+ROWS($B$7:$D66)-1,"")</f>
         <v>44499</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="E35" s="2"/>
+      <c r="F35" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F66)-1&lt;=$F$3,$B$3+ROWS($B$7:$F66)-1,"")</f>
         <v>44499</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="G35" s="2"/>
+      <c r="H35" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B35)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B35)-1,$J$5:$J$7),"")</f>
         <v>44483</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="3" t="n">
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B36)-1&lt;=$F$3,$B$3+ROWS($B$7:$B36)-1,"")</f>
         <v>44469</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="C36" s="2"/>
+      <c r="D36" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D67)-1&lt;=$F$3,$B$3+ROWS($B$7:$D67)-1,"")</f>
         <v>44500</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="E36" s="2"/>
+      <c r="F36" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F67)-1&lt;=$F$3,$B$3+ROWS($B$7:$F67)-1,"")</f>
         <v>44500</v>
       </c>
-      <c r="H36" s="3" t="n">
+      <c r="G36" s="2"/>
+      <c r="H36" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B36)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B36)-1,$J$5:$J$7),"")</f>
         <v>44484</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="3"/>
-      <c r="D37" s="3" t="n">
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D68)-1&lt;=$F$3,$B$3+ROWS($B$7:$D68)-1,"")</f>
         <v>44501</v>
       </c>
-      <c r="F37" s="3" t="n">
+      <c r="E37" s="2"/>
+      <c r="F37" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F68)-1&lt;=$F$3,$B$3+ROWS($B$7:$F68)-1,"")</f>
         <v>44501</v>
       </c>
-      <c r="H37" s="3" t="n">
+      <c r="G37" s="2"/>
+      <c r="H37" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B37)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B37)-1,$J$5:$J$7),"")</f>
         <v>44487</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D38" s="3" t="n">
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$D69)-1&lt;=$F$3,$B$3+ROWS($B$7:$D69)-1,"")</f>
         <v>44502</v>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="E38" s="2"/>
+      <c r="F38" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$F69)-1&lt;=$F$3,$B$3+ROWS($B$7:$F69)-1,"")</f>
         <v>44502</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="G38" s="2"/>
+      <c r="H38" s="4" t="n">
         <f aca="false">IF($B$3+ROWS($B$7:$B38)-1&lt;=$F$3,WORKDAY($B$3,ROWS($B$7:$B38)-1,$J$5:$J$7),"")</f>
         <v>44488</v>
       </c>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
